--- a/data/trans_orig/P20D1_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P20D1_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si durante su último ingreso estuvo acompañado/a por un hombre en 2023</t>
+          <t>Población según si durante su último ingreso estuvo acompañado/a por un hombre en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7424</t>
+          <t>7462</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14993</t>
+          <t>15097</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8337</t>
+          <t>8254</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13041</t>
+          <t>13336</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22106</t>
+          <t>21829</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>67,7%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>926</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7460</t>
+          <t>7659</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>322</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>3567</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1617</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8443</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,06%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8059</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9301</t>
+          <t>9106</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6524</t>
+          <t>6621</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14995</t>
+          <t>15282</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>47,4%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14277</t>
+          <t>14490</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25403</t>
+          <t>25539</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5174</t>
+          <t>4934</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>13877</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22335</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37167</t>
+          <t>36669</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>59,81%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>3247</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13589</t>
+          <t>12828</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7449</t>
+          <t>7458</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6287</t>
+          <t>6716</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>17586</t>
+          <t>17665</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,81%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1753</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9586</t>
+          <t>10458</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11160</t>
+          <t>10739</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21055</t>
+          <t>20957</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14528</t>
+          <t>13883</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29338</t>
+          <t>28777</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>46,94%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2721</t>
+          <t>2246</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9922</t>
+          <t>10145</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>675</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4659</t>
+          <t>4465</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>4565</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12845</t>
+          <t>13167</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>71,56%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>567</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7991</t>
+          <t>8466</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>478</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4230</t>
+          <t>4254</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>11213</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>60,94%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1554</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1857</t>
+          <t>1675</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6123</t>
+          <t>5719</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1487</t>
+          <t>1369</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>7378</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,09%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31502</t>
+          <t>32152</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46394</t>
+          <t>46933</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11153</t>
+          <t>11806</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22256</t>
+          <t>22573</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47423</t>
+          <t>47523</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>67844</t>
+          <t>66634</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>59,52%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8205</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21974</t>
+          <t>21394</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3512</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11096</t>
+          <t>10930</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13928</t>
+          <t>14101</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30048</t>
+          <t>29504</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4257</t>
+          <t>4017</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15365</t>
+          <t>14853</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20758</t>
+          <t>20382</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32740</t>
+          <t>32926</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25096</t>
+          <t>26473</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>43818</t>
+          <t>45332</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>40,49%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P20D1_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P20D1_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11821</t>
+          <t>12397</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7462</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15097</t>
+          <t>15965</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5790</t>
+          <t>7091</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3079</t>
+          <t>4220</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8254</t>
+          <t>10012</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>17611</t>
+          <t>19488</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13336</t>
+          <t>14701</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21829</t>
+          <t>24416</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>70,54%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>981</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7659</t>
+          <t>7522</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>341</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3567</t>
+          <t>3502</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>4198</t>
+          <t>4407</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1617</t>
+          <t>1753</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8401</t>
+          <t>8703</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,14%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>1469</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7998</t>
+          <t>8691</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6540</t>
+          <t>6774</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>4083</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>9658</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>10433</t>
+          <t>10715</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>7074</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15282</t>
+          <t>16038</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>46,34%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18745</t>
+          <t>19461</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18745</t>
+          <t>19461</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18745</t>
+          <t>19461</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>15150</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>15150</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>15150</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>32242</t>
+          <t>34611</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32242</t>
+          <t>34611</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32242</t>
+          <t>34611</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>20444</t>
+          <t>25267</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14490</t>
+          <t>19515</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25539</t>
+          <t>30232</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4934</t>
+          <t>6160</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13877</t>
+          <t>15237</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>29451</t>
+          <t>35625</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>27109</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36669</t>
+          <t>43621</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>62,5%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7623</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>3526</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12828</t>
+          <t>12865</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3705</t>
+          <t>3852</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1598</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7458</t>
+          <t>7488</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>11327</t>
+          <t>11350</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6716</t>
+          <t>6308</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>17665</t>
+          <t>17645</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>25,28%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4752</t>
+          <t>4788</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10458</t>
+          <t>10448</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15780</t>
+          <t>18034</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10739</t>
+          <t>13098</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20957</t>
+          <t>23545</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>20533</t>
+          <t>22822</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13883</t>
+          <t>15444</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28777</t>
+          <t>32446</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>46,49%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32819</t>
+          <t>37553</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32819</t>
+          <t>37553</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32819</t>
+          <t>37553</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28491</t>
+          <t>32245</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28491</t>
+          <t>32245</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28491</t>
+          <t>32245</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>61311</t>
+          <t>69798</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>61311</t>
+          <t>69798</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>61311</t>
+          <t>69798</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7205</t>
+          <t>7378</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2246</t>
+          <t>3016</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10145</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>3342</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>788</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4465</t>
+          <t>5946</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>9311</t>
+          <t>10719</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>6003</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13167</t>
+          <t>14872</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>72,47%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>3810</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>551</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8466</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>475</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4254</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5672</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11213</t>
+          <t>11420</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>55,64%</t>
         </is>
       </c>
     </row>
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3789</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5719</t>
+          <t>6992</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3788</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1369</t>
+          <t>1433</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>8254</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,22%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10712</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10712</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10712</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7689</t>
+          <t>9336</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7689</t>
+          <t>9336</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7689</t>
+          <t>9336</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>18401</t>
+          <t>20523</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>18401</t>
+          <t>20523</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>18401</t>
+          <t>20523</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>39471</t>
+          <t>45042</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32152</t>
+          <t>36025</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46933</t>
+          <t>52221</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>16902</t>
+          <t>20791</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11806</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22573</t>
+          <t>27332</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>56373</t>
+          <t>65833</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47523</t>
+          <t>54923</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>66634</t>
+          <t>76261</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>61,04%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14161</t>
+          <t>14430</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8522</t>
+          <t>8698</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21394</t>
+          <t>23205</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6666</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3566</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10930</t>
+          <t>12074</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>20827</t>
+          <t>21430</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14101</t>
+          <t>13691</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29504</t>
+          <t>30739</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>24,6%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8645</t>
+          <t>8730</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14853</t>
+          <t>15052</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>26109</t>
+          <t>28940</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20382</t>
+          <t>21682</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32926</t>
+          <t>35533</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>34754</t>
+          <t>37670</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>26473</t>
+          <t>28851</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>45332</t>
+          <t>48984</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>39,21%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>49677</t>
+          <t>56731</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49677</t>
+          <t>56731</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49677</t>
+          <t>56731</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>111954</t>
+          <t>124933</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>111954</t>
+          <t>124933</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>111954</t>
+          <t>124933</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
